--- a/data/trans_orig/IP18A01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18A01-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>12636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10233</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>19832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57615</t>
+          <t>58761</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66711</t>
+          <t>66961</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63823</t>
+          <t>63899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71313</t>
+          <t>71427</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126154</t>
+          <t>125621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136925</t>
+          <t>137069</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19702</t>
+          <t>18701</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34826</t>
+          <t>34823</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24887</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42308</t>
+          <t>42836</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48060</t>
+          <t>49086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72625</t>
+          <t>72388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>337500</t>
+          <t>337503</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>352624</t>
+          <t>353625</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367003</t>
+          <t>366475</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>384424</t>
+          <t>384891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>709012</t>
+          <t>709249</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733577</t>
+          <t>732551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22769</t>
+          <t>23419</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20645</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>22141</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39207</t>
+          <t>39497</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131525</t>
+          <t>130875</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143600</t>
+          <t>143590</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119276</t>
+          <t>119361</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130994</t>
+          <t>131455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255008</t>
+          <t>254718</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272185</t>
+          <t>272074</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>42169</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62606</t>
+          <t>63698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41265</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64874</t>
+          <t>63941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88957</t>
+          <t>89537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119181</t>
+          <t>119611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>535412</t>
+          <t>534320</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>557018</t>
+          <t>555849</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>558414</t>
+          <t>559347</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>582023</t>
+          <t>580859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1102125</t>
+          <t>1101695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1132349</t>
+          <t>1131769</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>14712</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>11681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24746</t>
+          <t>24944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71722</t>
+          <t>71935</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81647</t>
+          <t>81628</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63195</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73086</t>
+          <t>72807</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138934</t>
+          <t>138736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152665</t>
+          <t>151999</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30247</t>
+          <t>30194</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49719</t>
+          <t>49406</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37327</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59708</t>
+          <t>59145</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72474</t>
+          <t>72214</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101515</t>
+          <t>101119</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>371326</t>
+          <t>371639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>390798</t>
+          <t>390851</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>406624</t>
+          <t>407187</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>429005</t>
+          <t>429287</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>785862</t>
+          <t>786258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>814903</t>
+          <t>815163</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23845</t>
+          <t>24639</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22540</t>
+          <t>22256</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24525</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42787</t>
+          <t>42763</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>132221</t>
+          <t>131427</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144648</t>
+          <t>144605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141162</t>
+          <t>141446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154174</t>
+          <t>154283</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>276980</t>
+          <t>277004</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295242</t>
+          <t>295759</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52879</t>
+          <t>53923</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77802</t>
+          <t>77796</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57727</t>
+          <t>58142</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84675</t>
+          <t>83651</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117856</t>
+          <t>117903</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>152398</t>
+          <t>153264</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>586002</t>
+          <t>586008</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>610925</t>
+          <t>609881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>622345</t>
+          <t>623369</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>649293</t>
+          <t>648878</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1218426</t>
+          <t>1217560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1252968</t>
+          <t>1252921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13261</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>47837</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53917</t>
+          <t>53872</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53006</t>
+          <t>53221</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60420</t>
+          <t>60402</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103464</t>
+          <t>103752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113003</t>
+          <t>113080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38300</t>
+          <t>38697</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59547</t>
+          <t>60335</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25984</t>
+          <t>26433</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44735</t>
+          <t>45283</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69422</t>
+          <t>70277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97861</t>
+          <t>97956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>373478</t>
+          <t>372690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>394725</t>
+          <t>394328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>391203</t>
+          <t>390655</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>409954</t>
+          <t>409505</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>771102</t>
+          <t>771007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>799541</t>
+          <t>798686</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15607</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13270</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26580</t>
+          <t>27209</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20756</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37787</t>
+          <t>37851</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>137053</t>
+          <t>137175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147745</t>
+          <t>147531</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145097</t>
+          <t>144468</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158407</t>
+          <t>158249</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>286550</t>
+          <t>286486</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>303581</t>
+          <t>303380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48061</t>
+          <t>49014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73365</t>
+          <t>74082</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47364</t>
+          <t>47953</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70654</t>
+          <t>72760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102744</t>
+          <t>102758</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138204</t>
+          <t>135141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>566980</t>
+          <t>566263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>592284</t>
+          <t>591331</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>599027</t>
+          <t>596921</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>622317</t>
+          <t>621728</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1171821</t>
+          <t>1174884</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1207281</t>
+          <t>1207267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>365</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>15614</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>13286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57528</t>
+          <t>57826</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64134</t>
+          <t>64054</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84000</t>
+          <t>84503</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89774</t>
+          <t>89808</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144554</t>
+          <t>144201</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>152929</t>
+          <t>152967</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>933</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22814</t>
+          <t>21540</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26318</t>
+          <t>26404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51435</t>
+          <t>51664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57880</t>
+          <t>57508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18872</t>
+          <t>18602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87670</t>
+          <t>87530</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96679</t>
+          <t>96545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122152</t>
+          <t>121587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129056</t>
+          <t>129063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>213034</t>
+          <t>213304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>223728</t>
+          <t>224190</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP18A01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18A01-Estudios-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por vacunación en 2007 (tasa de respuesta: 99,78%)</t>
+          <t>Menores según si su última consulta médica fue por vacunación en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5469</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2627</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10566</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8179</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4436</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12636</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13476</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,46%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5469</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2629</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10157</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19832</t>
+          <t>20371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68587</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>63490</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>71429</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>63218</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>58761</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>66961</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>57921</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>66839</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>88,54%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,79%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68587</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>63899</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>71427</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,62%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>125621</t>
+          <t>125082</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137069</t>
+          <t>136794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>71397</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>71397</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>71397</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32907</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>25009</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41877</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>26747</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>18701</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>34823</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>19560</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>36402</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,18%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>32907</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>24420</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>42836</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49086</t>
+          <t>48679</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72388</t>
+          <t>71573</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>376404</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>367434</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>384302</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>521</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>345579</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>337503</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>353625</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>335924</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>352766</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,82%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,65%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,98%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>376404</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>366475</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>384891</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,96%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>709249</t>
+          <t>710064</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>732551</t>
+          <t>732958</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>409311</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>409311</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>409311</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>561</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>372326</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>372326</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>372326</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>409311</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>409311</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>409311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13810</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8685</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20777</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>16201</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10704</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23419</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10509</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>23602</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13810</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8466</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>20560</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22141</t>
+          <t>21758</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39497</t>
+          <t>38849</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>126111</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>119144</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>131236</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,79%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>138093</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>130875</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>143590</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>130692</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>143785</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,5%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,82%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>126111</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>119361</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>131455</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,13%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>254718</t>
+          <t>255366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272074</t>
+          <t>272457</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154294</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154294</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154294</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,64 +1752,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>52186</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41393</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>62749</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>51127</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>42169</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>63698</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>40701</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>62933</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,55%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>52186</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>42429</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>63941</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>6,81%</t>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89537</t>
+          <t>88530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119611</t>
+          <t>119171</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -1865,67 +1865,67 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>571102</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>560539</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>581895</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>815</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>546891</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>534320</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>555849</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>535085</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>557317</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,45%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>860</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>571102</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>559347</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>580859</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1101695</t>
+          <t>1102135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1131769</t>
+          <t>1132776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>623288</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>623288</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>623288</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>598018</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>598018</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>623288</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>623288</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>623288</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2141,13 +2141,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por vacunación en 2012 (tasa de respuesta: 98,1%)</t>
+          <t>Menores según si su última consulta médica fue por vacunación en 2012 (tasa de respuesta: 98,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8066</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3864</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14726</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19,13%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9272</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5066</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14759</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5092</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14911</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10,7%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8066</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4179</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14712</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11681</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24944</t>
+          <t>24941</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68920</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>62260</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>73122</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>80,87%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,98%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>77422</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>71935</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>81628</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>71783</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>81602</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>89,3%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,98%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68920</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>62274</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>72807</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>89,52%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138736</t>
+          <t>138739</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151999</t>
+          <t>152268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>76986</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>76986</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>76986</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>86694</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>86694</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>86694</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>76986</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>76986</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>76986</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>46922</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36721</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>59931</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>38620</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30194</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>49406</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>30242</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>49634</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,17%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,73%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>46922</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>37045</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>59145</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>10,06%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72214</t>
+          <t>70971</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101119</t>
+          <t>101742</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>419410</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>406401</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>429611</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>382425</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>371639</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>390851</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>371411</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>390803</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,83%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>419410</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>407187</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>429287</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,94%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>786258</t>
+          <t>785635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>815163</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466332</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466332</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466332</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>610</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>421045</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>421045</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>421045</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>466332</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>466332</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>466332</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15190</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9959</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22030</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>17216</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11461</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24639</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11638</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>25026</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,03%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15190</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9419</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>22256</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24008</t>
+          <t>24213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42763</t>
+          <t>42783</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148512</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>141672</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>153743</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>138850</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>131427</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>144605</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>131040</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>144428</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,97%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148512</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>141446</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>154283</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,72%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>277004</t>
+          <t>276984</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295759</t>
+          <t>295554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,43%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>163702</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>163702</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>163702</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>163702</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>163702</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>163702</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>70178</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>58653</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>84041</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>65108</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>53923</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>77796</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>52968</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>78747</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,81%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>70178</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>58142</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>83651</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117903</t>
+          <t>116415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>153264</t>
+          <t>155394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>636842</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>622979</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>648367</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,07%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>862</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>598696</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>586008</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>609881</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>585057</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>610836</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,19%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,28%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>636842</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>623369</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>648878</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,07%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1217560</t>
+          <t>1215430</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1252921</t>
+          <t>1254409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>707020</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>707020</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>707020</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>955</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>663804</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>663804</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>663804</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>707020</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>707020</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>707020</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3744,13 +3744,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por vacunación en 2016 (tasa de respuesta: 98,16%)</t>
+          <t>Menores según si su última consulta médica fue por vacunación en 2016 (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4450</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1827</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9952</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2905</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6823</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6847</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,31%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4450</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1663</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8844</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12973</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57615</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52113</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>60238</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>51755</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>47837</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53872</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>47813</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>53914</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,69%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>57615</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>53221</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>60402</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,83%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103752</t>
+          <t>104056</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113080</t>
+          <t>113071</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62065</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62065</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62065</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>54660</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>54660</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>54660</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62065</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>62065</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62065</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>34652</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>45038</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>48148</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>38697</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>60335</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>38677</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>59875</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,12%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>34652</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>26433</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>45283</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70277</t>
+          <t>69344</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97956</t>
+          <t>99338</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>401286</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>390900</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>410173</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,05%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,67%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>584</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>384877</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>372690</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>394328</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>373150</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>394348</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,88%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,06%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>401286</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>390655</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>409505</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,05%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>771007</t>
+          <t>769625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>798686</t>
+          <t>799619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>435938</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>435938</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>435938</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>655</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>433025</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>433025</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>433025</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>435938</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>435938</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>435938</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19520</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13381</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28265</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9195</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5129</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15485</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5158</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14669</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,02%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>19520</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>13428</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>27209</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37851</t>
+          <t>37247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>152157</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>143412</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158296</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>143465</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>137175</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>147531</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>137991</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>147502</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,98%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>152157</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>144468</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158249</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,63%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>286486</t>
+          <t>287090</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>303380</t>
+          <t>303643</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171677</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171677</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171677</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>152660</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>152660</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>152660</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171677</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171677</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171677</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>58621</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45971</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>72075</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>60248</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>49014</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>74082</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>72997</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,41%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>58621</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>47953</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>72760</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102758</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135141</t>
+          <t>137035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>611060</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>597606</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>623710</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>877</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>580097</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>566263</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>591331</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>567348</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>590682</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,59%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>611060</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>596921</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>621728</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1174884</t>
+          <t>1172990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1207267</t>
+          <t>1206442</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>965</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>640345</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>640345</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>640345</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5347,13 +5347,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por vacunación en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si su última consulta médica fue por vacunación en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3195</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>35,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3511</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,43%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3504</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>17,3%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3090</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>353</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8504</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5896</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>64,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5339</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3034</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>81,57%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4924</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5954</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>82,7%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>41,15%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8808</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6344</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9434</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,37%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>67,25%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>21</t>
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2573</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5291</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4605</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8412</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>81234</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78516</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82760</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>61633</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>57826</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>64054</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,05%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>87937</t>
+          <t>58801</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84503</t>
+          <t>54899</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89808</t>
+          <t>61379</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>149570</t>
+          <t>140035</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144201</t>
+          <t>135216</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>152967</t>
+          <t>142912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>868</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -6331,74 +6331,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27436</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23816</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>26182</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21540</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>78,24%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>24949</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>21161</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>26332</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>94,75%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>80,36%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>29503</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>26404</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>30909</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,45%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>85,43%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>80</t>
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>55687</t>
+          <t>52384</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51664</t>
+          <t>47404</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>54287</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4549</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2282</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8806</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7160</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3769</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12784</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,74%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18602</t>
+          <t>17885</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>117173</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>112916</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>119440</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>93154</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>87530</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>96545</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,86%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>126249</t>
+          <t>88674</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121587</t>
+          <t>83197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129063</t>
+          <t>92214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>219403</t>
+          <t>205847</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>213304</t>
+          <t>199349</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224190</t>
+          <t>209948</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
